--- a/BROMappings/Mapping BRO GLD Events.xlsx
+++ b/BROMappings/Mapping BRO GLD Events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/Meny_OS/trunk/Datamodels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/Meny_OS/trunk/BronDatamodel/BROMappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{095261ED-ABE2-49B7-9BF7-3FCA8EA64B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C362502-4182-4FAB-B2CA-FA91D5DEBAB6}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{6C14A7D8-3620-4B60-882E-67C4BBD26BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4AB0629-70FA-4C08-8C28-1C0BC5696D4F}"/>
   <bookViews>
-    <workbookView xWindow="-3810" yWindow="3930" windowWidth="23250" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
   <si>
     <t>BROBrondocument</t>
   </si>
@@ -54,12 +54,6 @@
     <t>BROGebeurtenisData</t>
   </si>
   <si>
-    <t>BROGebeurtenisWerkafspraak</t>
-  </si>
-  <si>
-    <t>BROGebeurtenisNieuw</t>
-  </si>
-  <si>
     <t>Correctie (attribuut)</t>
   </si>
   <si>
@@ -166,22 +160,38 @@
   </si>
   <si>
     <t>De BRO maakt geen onderscheid tussen correcties van attribuutwaarden en metingen</t>
+  </si>
+  <si>
+    <t>[Categorical]</t>
+  </si>
+  <si>
+    <t>[String]</t>
+  </si>
+  <si>
+    <t>BronOmschrijving</t>
+  </si>
+  <si>
+    <t>Beoordelen</t>
+  </si>
+  <si>
+    <t>Metingen beoordeeld</t>
+  </si>
+  <si>
+    <t>GLD_Status</t>
+  </si>
+  <si>
+    <t>GLD-Beoordeling</t>
+  </si>
+  <si>
+    <t>GLD_Status is geen echt brondocument, maar een optie. Indien een observatie voorlopig geregistreerd was, dan betreft dit een vervangverzoek. Zo niet, dan betreft het een aanvulling. Het betreft alle observaties tot dan toe in eens</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -201,16 +211,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF005E6A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85C9EB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -229,103 +265,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -365,19 +304,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -422,6 +348,76 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -433,36 +429,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,10 +487,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -747,247 +752,263 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" customWidth="1"/>
-    <col min="7" max="7" width="102.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="62.85546875" customWidth="1"/>
+    <col min="6" max="6" width="107.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="21"/>
+      <c r="F9" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="11"/>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17" t="s">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="11"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
